--- a/data/gravel/Lapierre Crosshill CF 2025.xlsx
+++ b/data/gravel/Lapierre Crosshill CF 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25EA0CC-E918-FF44-B242-550024447561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D850969-AB58-B04F-A29C-C5E6613ADDEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="960" windowWidth="26020" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25500" yWindow="-22180" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -251,18 +251,9 @@
     <t>rigid</t>
   </si>
   <si>
-    <t>threaded</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
-  </si>
-  <si>
     <t>carbon</t>
   </si>
   <si>
@@ -272,21 +263,12 @@
     <t>front_center</t>
   </si>
   <si>
-    <t>a8:g34</t>
-  </si>
-  <si>
     <t>Lapierre</t>
   </si>
   <si>
     <t>Crosshill CF</t>
   </si>
   <si>
-    <t>https://www.lapierrebikes.com/nl-en/v/bikes/?attrModelYears=2025&amp;attrProductLine=Crosshill%20CF</t>
-  </si>
-  <si>
-    <t>Size</t>
-  </si>
-  <si>
     <t>XS</t>
   </si>
   <si>
@@ -305,43 +287,79 @@
     <t>XXL</t>
   </si>
   <si>
-    <t>Top tube</t>
-  </si>
-  <si>
-    <t>Seat tube</t>
-  </si>
-  <si>
-    <t>Head tube</t>
-  </si>
-  <si>
-    <t>Head angle</t>
-  </si>
-  <si>
-    <t>Seat angle</t>
-  </si>
-  <si>
-    <t>Chainstay</t>
-  </si>
-  <si>
-    <t>BB Drop</t>
-  </si>
-  <si>
-    <t>Wheelbase</t>
-  </si>
-  <si>
-    <t>Reach</t>
-  </si>
-  <si>
-    <t>Stack</t>
-  </si>
-  <si>
     <t>semi-integrated</t>
   </si>
   <si>
-    <t>est 425</t>
-  </si>
-  <si>
-    <t>euro</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>ST (mm)</t>
+  </si>
+  <si>
+    <t>TT (mm)</t>
+  </si>
+  <si>
+    <t>HA (°)</t>
+  </si>
+  <si>
+    <t>SA (°)</t>
+  </si>
+  <si>
+    <t>RC DSC (mm)</t>
+  </si>
+  <si>
+    <t>HT (mm)</t>
+  </si>
+  <si>
+    <t>BB (mm)</t>
+  </si>
+  <si>
+    <t>FRK Length (mm)</t>
+  </si>
+  <si>
+    <t>FRK Offset (mm)</t>
+  </si>
+  <si>
+    <t>Stack (mm)</t>
+  </si>
+  <si>
+    <t>Reach (mm)</t>
+  </si>
+  <si>
+    <t>WB DSC (mm)</t>
+  </si>
+  <si>
+    <t>USER (cm)</t>
+  </si>
+  <si>
+    <t>150–162</t>
+  </si>
+  <si>
+    <t>160–172</t>
+  </si>
+  <si>
+    <t>170–182</t>
+  </si>
+  <si>
+    <t>180–190</t>
+  </si>
+  <si>
+    <t>188–195</t>
+  </si>
+  <si>
+    <t>&gt;192</t>
+  </si>
+  <si>
+    <t>https://www.lapierrebikes.com/nl-en/crosshill/</t>
+  </si>
+  <si>
+    <t>press fit</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>a8:g32</t>
   </si>
 </sst>
 </file>
@@ -413,7 +431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -423,6 +441,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -719,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -730,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -738,7 +757,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -762,7 +781,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -770,7 +789,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -778,181 +797,181 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C9" s="6">
-        <v>529</v>
+        <v>440</v>
       </c>
       <c r="D9" s="6">
-        <v>541</v>
+        <v>460</v>
       </c>
       <c r="E9" s="6">
-        <v>552</v>
+        <v>490</v>
       </c>
       <c r="F9" s="6">
-        <v>570</v>
+        <v>520</v>
       </c>
       <c r="G9" s="6">
-        <v>585</v>
+        <v>550</v>
       </c>
       <c r="H9">
-        <v>597</v>
+        <v>580</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C10" s="6">
-        <v>440</v>
+        <v>529</v>
       </c>
       <c r="D10" s="6">
-        <v>460</v>
+        <v>541</v>
       </c>
       <c r="E10" s="6">
-        <v>490</v>
+        <v>552</v>
       </c>
       <c r="F10" s="6">
-        <v>520</v>
+        <v>570</v>
       </c>
       <c r="G10" s="6">
-        <v>550</v>
+        <v>585</v>
       </c>
       <c r="H10">
-        <v>580</v>
+        <v>601</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C11" s="6">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="D11" s="6">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="E11" s="6">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="F11" s="6">
-        <v>150</v>
+        <v>71.5</v>
       </c>
       <c r="G11" s="6">
-        <v>170</v>
+        <v>71.5</v>
       </c>
       <c r="H11">
-        <v>195</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C12" s="6">
-        <v>70.5</v>
+        <v>73.5</v>
       </c>
       <c r="D12" s="6">
-        <v>71</v>
+        <v>73.5</v>
       </c>
       <c r="E12" s="6">
-        <v>71</v>
+        <v>73.5</v>
       </c>
       <c r="F12" s="6">
-        <v>71.5</v>
+        <v>73</v>
       </c>
       <c r="G12" s="6">
-        <v>71.5</v>
+        <v>72.5</v>
       </c>
       <c r="H12">
-        <v>71.5</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C13" s="6">
-        <v>73.5</v>
+        <v>430</v>
       </c>
       <c r="D13" s="6">
-        <v>73.5</v>
+        <v>430</v>
       </c>
       <c r="E13" s="6">
-        <v>73.5</v>
+        <v>430</v>
       </c>
       <c r="F13" s="6">
-        <v>73</v>
+        <v>430</v>
       </c>
       <c r="G13" s="6">
-        <v>72.5</v>
+        <v>430</v>
       </c>
       <c r="H13">
-        <v>72.5</v>
+        <v>430</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="6">
         <v>95</v>
       </c>
-      <c r="C14" s="6">
-        <v>430</v>
-      </c>
       <c r="D14" s="6">
-        <v>430</v>
+        <v>115</v>
       </c>
       <c r="E14" s="6">
-        <v>430</v>
+        <v>130</v>
       </c>
       <c r="F14" s="6">
-        <v>430</v>
+        <v>150</v>
       </c>
       <c r="G14" s="6">
-        <v>430</v>
+        <v>170</v>
       </c>
       <c r="H14">
-        <v>430</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -960,7 +979,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C15" s="6">
         <v>71</v>
@@ -972,65 +991,65 @@
         <v>71</v>
       </c>
       <c r="F15" s="6">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G15" s="6">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H15">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C16" s="6">
-        <v>1007</v>
+        <v>425</v>
       </c>
       <c r="D16" s="6">
-        <v>1016</v>
+        <v>425</v>
       </c>
       <c r="E16" s="6">
-        <v>1027</v>
+        <v>425</v>
       </c>
       <c r="F16" s="6">
-        <v>1036</v>
+        <v>425</v>
       </c>
       <c r="G16" s="6">
-        <v>1045</v>
+        <v>425</v>
       </c>
       <c r="H16">
-        <v>1062</v>
+        <v>425</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C17" s="6">
-        <v>367</v>
+        <v>45</v>
       </c>
       <c r="D17" s="6">
-        <v>373</v>
+        <v>45</v>
       </c>
       <c r="E17" s="6">
-        <v>380</v>
+        <v>45</v>
       </c>
       <c r="F17" s="6">
-        <v>386</v>
+        <v>45</v>
       </c>
       <c r="G17" s="6">
-        <v>390</v>
+        <v>45</v>
       </c>
       <c r="H17">
-        <v>398</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1038,7 +1057,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C18">
         <v>546</v>
@@ -1061,42 +1080,76 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="6">
+        <v>367</v>
+      </c>
+      <c r="D19" s="6">
+        <v>373</v>
+      </c>
+      <c r="E19" s="6">
+        <v>380</v>
+      </c>
+      <c r="F19" s="6">
+        <v>386</v>
+      </c>
+      <c r="G19" s="6">
+        <v>390</v>
+      </c>
+      <c r="H19">
+        <v>398</v>
+      </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="1"/>
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20">
+        <v>1007</v>
+      </c>
+      <c r="D20">
+        <v>1016</v>
+      </c>
+      <c r="E20">
+        <v>1027</v>
+      </c>
+      <c r="F20">
+        <v>1036</v>
+      </c>
+      <c r="G20">
+        <v>1045</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1062</v>
+      </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>15</v>
+      <c r="A23" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
-      <c r="I23" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="I23" s="1"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -1140,6 +1193,9 @@
       <c r="G28">
         <v>700</v>
       </c>
+      <c r="H28">
+        <v>700</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -1163,6 +1219,9 @@
       <c r="G29">
         <v>38</v>
       </c>
+      <c r="H29">
+        <v>38</v>
+      </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -1186,6 +1245,9 @@
       <c r="G30">
         <v>45</v>
       </c>
+      <c r="H30">
+        <v>45</v>
+      </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -1194,12 +1256,24 @@
       <c r="B31" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
+      <c r="C31" s="9">
+        <v>150</v>
+      </c>
+      <c r="D31" s="9">
+        <v>160</v>
+      </c>
+      <c r="E31" s="9">
+        <v>170</v>
+      </c>
+      <c r="F31" s="9">
+        <v>180</v>
+      </c>
+      <c r="G31" s="9">
+        <v>188</v>
+      </c>
+      <c r="H31" s="9">
+        <v>192</v>
+      </c>
       <c r="I31" s="3"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
@@ -1209,292 +1283,308 @@
       <c r="B32" t="s">
         <v>28</v>
       </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
+      <c r="C32" s="9">
+        <v>162</v>
+      </c>
+      <c r="D32" s="9">
+        <v>172</v>
+      </c>
+      <c r="E32" s="9">
+        <v>182</v>
+      </c>
+      <c r="F32" s="9">
+        <v>190</v>
+      </c>
+      <c r="G32" s="9">
+        <v>195</v>
+      </c>
+      <c r="H32" s="9">
+        <v>200</v>
+      </c>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C33" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" t="s">
+        <v>100</v>
+      </c>
+      <c r="E33" t="s">
+        <v>101</v>
+      </c>
+      <c r="F33" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" t="s">
+        <v>103</v>
+      </c>
+      <c r="H33" t="s">
+        <v>104</v>
+      </c>
+      <c r="I33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>68</v>
-      </c>
-      <c r="B38" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>70</v>
-      </c>
-      <c r="B39" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>31</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="B41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B43">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="B44" s="1"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>36</v>
-      </c>
-      <c r="B45">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="B47">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="B48">
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49">
-        <v>142</v>
+        <v>42</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50">
-        <v>100</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>72</v>
+        <v>44</v>
+      </c>
+      <c r="B51">
+        <v>27.2</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53">
-        <v>27.2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>50</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B59" s="1"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>51</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>100</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B60" s="1"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>52</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>53</v>
-      </c>
-      <c r="B62" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>55</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
+        <v>57</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+      <c r="B65" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>57</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>73</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>58</v>
-      </c>
-      <c r="B67" s="1">
-        <v>2</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>59</v>
-      </c>
-      <c r="B68" s="1"/>
+        <v>61</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>60</v>
-      </c>
-      <c r="B69" s="1"/>
+        <v>62</v>
+      </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>61</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
+      </c>
+      <c r="B70">
+        <v>2799</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>62</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="B71" s="1"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>63</v>
-      </c>
-      <c r="B72">
-        <v>2799</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>64</v>
-      </c>
-      <c r="B73" s="1"/>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
         <v>65</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>102</v>
+      <c r="B72" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Lapierre Crosshill CF 2025.xlsx
+++ b/data/gravel/Lapierre Crosshill CF 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D850969-AB58-B04F-A29C-C5E6613ADDEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26BF1A8-1CB6-FF4B-8581-4C2204A01F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25500" yWindow="-22180" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,9 @@
   </si>
   <si>
     <t>a8:g32</t>
+  </si>
+  <si>
+    <t>https://adfnjoxprq.cloudimg.io/v7/_lapierre_prod/media/b2/73/83/1725610142/Crosshill%20CF%206.0%20AXS%20-%20Lapierre%20MY25%20-%20LCFTC%20-%20Cover.png</t>
   </si>
 </sst>
 </file>
@@ -784,6 +787,11 @@
         <v>105</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Lapierre Crosshill CF 2025.xlsx
+++ b/data/gravel/Lapierre Crosshill CF 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26BF1A8-1CB6-FF4B-8581-4C2204A01F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75020BE8-661A-FA4C-87D5-14A33D4D46DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25500" yWindow="-22180" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -363,6 +363,12 @@
   </si>
   <si>
     <t>https://adfnjoxprq.cloudimg.io/v7/_lapierre_prod/media/b2/73/83/1725610142/Crosshill%20CF%206.0%20AXS%20-%20Lapierre%20MY25%20-%20LCFTC%20-%20Cover.png</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Dijon, France</t>
   </si>
 </sst>
 </file>
@@ -741,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1595,6 +1601,14 @@
         <v>107</v>
       </c>
     </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>110</v>
+      </c>
+      <c r="B73" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Lapierre Crosshill CF 2025.xlsx
+++ b/data/gravel/Lapierre Crosshill CF 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75020BE8-661A-FA4C-87D5-14A33D4D46DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0882AC97-4264-7E42-B625-FC76F560CD2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -369,6 +369,9 @@
   </si>
   <si>
     <t>Dijon, France</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -1512,7 +1515,9 @@
       <c r="A59" t="s">
         <v>52</v>
       </c>
-      <c r="B59" s="1"/>
+      <c r="B59" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">

--- a/data/gravel/Lapierre Crosshill CF 2025.xlsx
+++ b/data/gravel/Lapierre Crosshill CF 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0882AC97-4264-7E42-B625-FC76F560CD2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40024495-1698-0043-85BC-8AC959AB1C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,24 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -750,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1451,166 +1469,196 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51">
-        <v>27.2</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B57">
+        <v>27.2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>52</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>112</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>53</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>55</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>58</v>
-      </c>
-      <c r="B65" s="1">
-        <v>2</v>
+        <v>52</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>60</v>
-      </c>
-      <c r="B67" s="1"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>61</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>63</v>
-      </c>
-      <c r="B70">
-        <v>2799</v>
+        <v>57</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>64</v>
-      </c>
-      <c r="B71" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="B71" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>65</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>107</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B72" s="1"/>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>60</v>
+      </c>
+      <c r="B73" s="1"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>63</v>
+      </c>
+      <c r="B76">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B77" s="1"/>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>110</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>111</v>
       </c>
     </row>
